--- a/05-Regression/Regression-Test-Suite.xlsx
+++ b/05-Regression/Regression-Test-Suite.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -557,7 +557,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>REG-002</t>
+          <t>REG-001</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Auth module change</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Passes critical flow</t>
+          <t>REG-001.png</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Not executed — no Android environment available</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>REG-003</t>
+          <t>REG-002</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -611,17 +611,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Catalog backend change</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Passes critical flow</t>
+          <t>REG-002.png</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Not executed — no Android environment available</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>REG-004</t>
+          <t>REG-003</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -650,17 +650,17 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Sorting algorithm change</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Passes critical flow</t>
+          <t>REG-003.png</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Not executed — no Android environment available</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>REG-005</t>
+          <t>REG-004</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>UI layout update</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Passes critical flow</t>
+          <t>REG-004.png</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Not executed — no Android environment available</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>REG-006</t>
+          <t>REG-005</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Cart logic update</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Passes critical flow</t>
+          <t>REG-005.png</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Not executed — no Android environment available</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -752,7 +752,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>REG-007</t>
+          <t>REG-006</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Cart logic update</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Passes critical flow</t>
+          <t>REG-006.png</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Not executed — no Android environment available</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>REG-008</t>
+          <t>REG-007</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -806,17 +806,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Auth requirement change</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Passes critical flow</t>
+          <t>REG-007.png</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Not executed — no Android environment available</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>REG-009</t>
+          <t>REG-008</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -845,17 +845,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Address validation update</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Passes critical flow</t>
+          <t>REG-008.png</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Not executed — no Android environment available</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>REG-010</t>
+          <t>REG-009</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -884,17 +884,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Payment gateway update</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Passes critical flow</t>
+          <t>REG-009.png</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Not executed — no Android environment available</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -908,7 +908,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>REG-011</t>
+          <t>REG-010</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Order processing update</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Passes critical flow</t>
+          <t>REG-010.png</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Not executed — no Android environment available</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>REG-012</t>
+          <t>REG-011</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -962,17 +962,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Order confirmation update</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Passes critical flow</t>
+          <t>REG-011.png</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Not executed — no Android environment available</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -982,6 +982,28 @@
       </c>
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REG-012</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>REG-012.png</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
